--- a/etsy/adhd-budget/Budget-TDAH.xlsx
+++ b/etsy/adhd-budget/Budget-TDAH.xlsx
@@ -121,7 +121,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -130,8 +130,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F6F4EF"/>
-        <bgColor rgb="00F6F4EF"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -144,12 +144,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFF4C2"/>
         <bgColor rgb="00FFF4C2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -193,16 +187,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D9D4C7"/>
+        <color rgb="00D5DBDB"/>
       </left>
       <right style="thin">
-        <color rgb="00D9D4C7"/>
+        <color rgb="00D5DBDB"/>
       </right>
       <top style="thin">
-        <color rgb="00D9D4C7"/>
+        <color rgb="00D5DBDB"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D9D4C7"/>
+        <color rgb="00D5DBDB"/>
       </bottom>
     </border>
   </borders>
@@ -220,13 +214,13 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="1" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="13" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="14" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="13" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="14" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -234,11 +228,16 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="6" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="7" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -246,9 +245,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -262,13 +258,13 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -720,7 +716,7 @@
       <c r="A2" s="1" t="n"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>L’argent en un coup d’œil</t>
+          <t>Vue d'ensemble</t>
         </is>
       </c>
       <c r="C2" s="1" t="n"/>
@@ -843,7 +839,7 @@
         <v/>
       </c>
       <c r="D8" s="11">
-        <f>SUM(Factures!$C$6:$C$30)-SUMIFS(Factures!$C$6:$C$30,Factures!$E$6:$E$30,TRUE)</f>
+        <f>SUM(Factures!$C$6:$C$30)-SUMIFS(Factures!$C$6:$C$30,Factures!$E$6:$E$30,"Oui")</f>
         <v/>
       </c>
       <c r="E8" s="10">
@@ -957,7 +953,7 @@
       </c>
       <c r="G13" s="1" t="n"/>
       <c r="H13" s="21">
-        <f>COUNTIFS(Factures!$F$6:$F$30,"Dans*")&amp;" facture(s) à payer dans les 3 jours"</f>
+        <f>IF((COUNTIFS(Factures!$F$6:$F$30,"Dans*")+COUNTIFS(Factures!$F$6:$F$30,"Aujourd'hui"))=0,"Aucune facture à payer dans les 3 jours",IF((COUNTIFS(Factures!$F$6:$F$30,"Dans*")+COUNTIFS(Factures!$F$6:$F$30,"Aujourd'hui"))=1,"1 facture",(COUNTIFS(Factures!$F$6:$F$30,"Dans*")+COUNTIFS(Factures!$F$6:$F$30,"Aujourd'hui"))&amp;" factures")&amp;" à payer dans les 3 jours")</f>
         <v/>
       </c>
       <c r="I13" s="1" t="n"/>
@@ -1012,7 +1008,7 @@
       </c>
       <c r="G15" s="1" t="n"/>
       <c r="H15" s="22">
-        <f>COUNTIFS(Factures!$F$6:$F$30,"⚠*")&amp;" facture(s) en retard"</f>
+        <f>IF(COUNTIFS(Factures!$F$6:$F$30,"En retard")=0,"Aucune facture en retard",IF(COUNTIFS(Factures!$F$6:$F$30,"En retard")=1,"1 facture en retard",COUNTIFS(Factures!$F$6:$F$30,"En retard")&amp;" factures en retard"))</f>
         <v/>
       </c>
       <c r="I15" s="1" t="n"/>
@@ -1067,7 +1063,7 @@
       </c>
       <c r="G17" s="1" t="n"/>
       <c r="H17" s="23">
-        <f>COUNTIFS(Envies!$E$6:$E$30,"⏳*")&amp;" envie(s) en attente sur votre liste"</f>
+        <f>IF(COUNTIFS(Envies!$E$6:$E$30,"Encore*")=0,"Aucune envie en attente",IF(COUNTIFS(Envies!$E$6:$E$30,"Encore*")=1,"1 envie",COUNTIFS(Envies!$E$6:$E$30,"Encore*")&amp;" envies")&amp;" en attente sur votre liste")</f>
         <v/>
       </c>
       <c r="I17" s="1" t="n"/>
@@ -1829,6 +1825,21 @@
     </cfRule>
     <cfRule type="expression" priority="3" dxfId="2">
       <formula>AND($C13&gt;0,$D13/$C13&gt;0.8,$D13/$C13&lt;=1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H13">
+    <cfRule type="expression" priority="4" dxfId="3">
+      <formula>LEFT(H13,6)="Aucune"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H15">
+    <cfRule type="expression" priority="5" dxfId="3">
+      <formula>LEFT(H15,6)="Aucune"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H17">
+    <cfRule type="expression" priority="6" dxfId="3">
+      <formula>LEFT(H17,6)="Aucune"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
@@ -1865,7 +1876,7 @@
       <c r="A2" s="1" t="n"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Commencer ici : 3 étapes, 5 minutes</t>
+          <t>Commencer ici</t>
         </is>
       </c>
       <c r="C2" s="1" t="n"/>
@@ -1875,7 +1886,7 @@
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Tapez uniquement dans les cases JAUNES. Tout le reste se remplit tout seul.</t>
+          <t>Tapez uniquement dans les cases jaunes. Tout le reste est calculé.</t>
         </is>
       </c>
       <c r="C3" s="1" t="n"/>
@@ -1916,7 +1927,7 @@
       </c>
       <c r="C7" s="26" t="inlineStr">
         <is>
-          <t>Onglet Factures : listez vos factures une seule fois (montant + jour d’échéance).</t>
+          <t>Onglet Factures : listez vos factures une seule fois, avec le montant et le jour d'échéance.</t>
         </is>
       </c>
       <c r="D7" s="1" t="n"/>
@@ -1936,7 +1947,7 @@
       </c>
       <c r="C9" s="26" t="inlineStr">
         <is>
-          <t>Onglet Journal : à chaque dépense ou rentrée d’argent, ajoutez UNE ligne : date, montant, catégorie.</t>
+          <t>Onglet Journal : à chaque dépense ou rentrée d'argent, ajoutez une ligne avec la date, le montant et la catégorie.</t>
         </is>
       </c>
       <c r="D9" s="1" t="n"/>
@@ -1963,12 +1974,12 @@
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C13" s="26" t="inlineStr">
         <is>
-          <t>Tableau de bord : choisissez le mois. Le grand chiffre, c’est ce que vous pouvez dépenser par jour sans risque.</t>
+          <t>Tableau de bord : choisissez le mois. Le grand chiffre indique ce que vous pouvez dépenser par jour jusqu'à la fin du mois.</t>
         </is>
       </c>
       <c r="D13" s="1" t="n"/>
@@ -1983,12 +1994,12 @@
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>⏳</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C15" s="26" t="inlineStr">
         <is>
-          <t>Envies : envie d’acheter quelque chose ? Mettez-le ici 48 heures d’abord.</t>
+          <t>Envies : quand vous voulez acheter quelque chose, notez-le ici et attendez 48 heures.</t>
         </is>
       </c>
       <c r="D15" s="1" t="n"/>
@@ -2003,12 +2014,12 @@
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>🎯</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C17" s="26" t="inlineStr">
         <is>
-          <t>Objectifs : regardez vos barres d’épargne se remplir.</t>
+          <t>Objectifs : mettez à jour ce que vous avez épargné et les barres se remplissent.</t>
         </is>
       </c>
       <c r="D17" s="1" t="n"/>
@@ -2036,7 +2047,7 @@
       <c r="B21" s="1" t="n"/>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Astuce : les lignes d’exemple (Journal, Factures, Objectifs) montrent comment ça marche. Supprimez-les et ajoutez les vôtres.</t>
+          <t>Les lignes d'exemple du Journal, des Factures et des Objectifs montrent comment ça marche. Supprimez-les et ajoutez les vôtres.</t>
         </is>
       </c>
       <c r="D21" s="1" t="n"/>
@@ -2052,7 +2063,7 @@
       <c r="B23" s="1" t="n"/>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Fonctionne dans Google Sheets (Fichier → Importer, ou ouvrez le fichier dans Drive) et dans Microsoft Excel.</t>
+          <t>Fonctionne dans Google Sheets (Fichier &gt; Importer, ou ouvrez le fichier depuis Drive) et dans Microsoft Excel.</t>
         </is>
       </c>
       <c r="D23" s="1" t="n"/>
@@ -3170,7 +3181,7 @@
       <c r="A2" s="1" t="n"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Journal : une ligne par mouvement d’argent</t>
+          <t>Journal : une ligne par achat ou rentrée d'argent</t>
         </is>
       </c>
       <c r="C2" s="1" t="n"/>
@@ -3183,7 +3194,7 @@
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Date · Montant · Type · Catégorie · Note. C’est tout.</t>
+          <t>Date, montant, type, catégorie, et une note si vous voulez.</t>
         </is>
       </c>
       <c r="C3" s="1" t="n"/>
@@ -3471,7 +3482,7 @@
       </c>
       <c r="F15" s="27" t="inlineStr">
         <is>
-          <t>Chaussures (passées par la liste Envies !)</t>
+          <t>Chaussures, passées par la liste Envies</t>
         </is>
       </c>
       <c r="G15" s="1" t="n"/>
@@ -4141,7 +4152,7 @@
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Mettez « Payée » à TRUE chaque mois. Les couleurs préviennent avant l’échéance.</t>
+          <t>Chaque mois, choisissez Oui quand une facture est payée. Les couleurs préviennent avant l'échéance.</t>
         </is>
       </c>
       <c r="C3" s="1" t="n"/>
@@ -4173,7 +4184,7 @@
       </c>
       <c r="D5" s="15" t="inlineStr">
         <is>
-          <t>Jour d’échéance</t>
+          <t>Jour d'échéance</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -4201,11 +4212,13 @@
       <c r="D6" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="31" t="b">
-        <v>1</v>
+      <c r="E6" s="31" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
       <c r="F6" s="32">
-        <f>IF(B6="","",IF(E6=TRUE,"✓ Payée",IF(D6&lt;DAY(TODAY()),"⚠ EN RETARD",IF(D6-DAY(TODAY())&lt;=3,"Dans "&amp;(D6-DAY(TODAY()))&amp;" jour(s)","Le "&amp;D6))))</f>
+        <f>IF(B6="","",IF(E6="Oui","Payée",IF(D6&lt;DAY(TODAY()),"En retard",IF((D6-DAY(TODAY()))=0,"Aujourd'hui",IF((D6-DAY(TODAY()))&lt;=3,"Dans "&amp;(D6-DAY(TODAY()))&amp;IF((D6-DAY(TODAY()))&lt;=1," jour"," jours"),"Le "&amp;D6)))))</f>
         <v/>
       </c>
       <c r="G6" s="1" t="n"/>
@@ -4223,11 +4236,13 @@
       <c r="D7" s="30" t="n">
         <v>29</v>
       </c>
-      <c r="E7" s="31" t="b">
-        <v>0</v>
+      <c r="E7" s="31" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
       <c r="F7" s="32">
-        <f>IF(B7="","",IF(E7=TRUE,"✓ Payée",IF(D7&lt;DAY(TODAY()),"⚠ EN RETARD",IF(D7-DAY(TODAY())&lt;=3,"Dans "&amp;(D7-DAY(TODAY()))&amp;" jour(s)","Le "&amp;D7))))</f>
+        <f>IF(B7="","",IF(E7="Oui","Payée",IF(D7&lt;DAY(TODAY()),"En retard",IF((D7-DAY(TODAY()))=0,"Aujourd'hui",IF((D7-DAY(TODAY()))&lt;=3,"Dans "&amp;(D7-DAY(TODAY()))&amp;IF((D7-DAY(TODAY()))&lt;=1," jour"," jours"),"Le "&amp;D7)))))</f>
         <v/>
       </c>
       <c r="G7" s="1" t="n"/>
@@ -4245,11 +4260,13 @@
       <c r="D8" s="30" t="n">
         <v>15</v>
       </c>
-      <c r="E8" s="31" t="b">
-        <v>1</v>
+      <c r="E8" s="31" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
       <c r="F8" s="32">
-        <f>IF(B8="","",IF(E8=TRUE,"✓ Payée",IF(D8&lt;DAY(TODAY()),"⚠ EN RETARD",IF(D8-DAY(TODAY())&lt;=3,"Dans "&amp;(D8-DAY(TODAY()))&amp;" jour(s)","Le "&amp;D8))))</f>
+        <f>IF(B8="","",IF(E8="Oui","Payée",IF(D8&lt;DAY(TODAY()),"En retard",IF((D8-DAY(TODAY()))=0,"Aujourd'hui",IF((D8-DAY(TODAY()))&lt;=3,"Dans "&amp;(D8-DAY(TODAY()))&amp;IF((D8-DAY(TODAY()))&lt;=1," jour"," jours"),"Le "&amp;D8)))))</f>
         <v/>
       </c>
       <c r="G8" s="1" t="n"/>
@@ -4267,11 +4284,13 @@
       <c r="D9" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="E9" s="31" t="b">
-        <v>0</v>
+      <c r="E9" s="31" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
       <c r="F9" s="32">
-        <f>IF(B9="","",IF(E9=TRUE,"✓ Payée",IF(D9&lt;DAY(TODAY()),"⚠ EN RETARD",IF(D9-DAY(TODAY())&lt;=3,"Dans "&amp;(D9-DAY(TODAY()))&amp;" jour(s)","Le "&amp;D9))))</f>
+        <f>IF(B9="","",IF(E9="Oui","Payée",IF(D9&lt;DAY(TODAY()),"En retard",IF((D9-DAY(TODAY()))=0,"Aujourd'hui",IF((D9-DAY(TODAY()))&lt;=3,"Dans "&amp;(D9-DAY(TODAY()))&amp;IF((D9-DAY(TODAY()))&lt;=1," jour"," jours"),"Le "&amp;D9)))))</f>
         <v/>
       </c>
       <c r="G9" s="1" t="n"/>
@@ -4289,11 +4308,13 @@
       <c r="D10" s="30" t="n">
         <v>24</v>
       </c>
-      <c r="E10" s="31" t="b">
-        <v>0</v>
+      <c r="E10" s="31" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
       <c r="F10" s="32">
-        <f>IF(B10="","",IF(E10=TRUE,"✓ Payée",IF(D10&lt;DAY(TODAY()),"⚠ EN RETARD",IF(D10-DAY(TODAY())&lt;=3,"Dans "&amp;(D10-DAY(TODAY()))&amp;" jour(s)","Le "&amp;D10))))</f>
+        <f>IF(B10="","",IF(E10="Oui","Payée",IF(D10&lt;DAY(TODAY()),"En retard",IF((D10-DAY(TODAY()))=0,"Aujourd'hui",IF((D10-DAY(TODAY()))&lt;=3,"Dans "&amp;(D10-DAY(TODAY()))&amp;IF((D10-DAY(TODAY()))&lt;=1," jour"," jours"),"Le "&amp;D10)))))</f>
         <v/>
       </c>
       <c r="G10" s="1" t="n"/>
@@ -4311,11 +4332,13 @@
       <c r="D11" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="E11" s="31" t="b">
-        <v>1</v>
+      <c r="E11" s="31" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
       <c r="F11" s="32">
-        <f>IF(B11="","",IF(E11=TRUE,"✓ Payée",IF(D11&lt;DAY(TODAY()),"⚠ EN RETARD",IF(D11-DAY(TODAY())&lt;=3,"Dans "&amp;(D11-DAY(TODAY()))&amp;" jour(s)","Le "&amp;D11))))</f>
+        <f>IF(B11="","",IF(E11="Oui","Payée",IF(D11&lt;DAY(TODAY()),"En retard",IF((D11-DAY(TODAY()))=0,"Aujourd'hui",IF((D11-DAY(TODAY()))&lt;=3,"Dans "&amp;(D11-DAY(TODAY()))&amp;IF((D11-DAY(TODAY()))&lt;=1," jour"," jours"),"Le "&amp;D11)))))</f>
         <v/>
       </c>
       <c r="G11" s="1" t="n"/>
@@ -4327,7 +4350,7 @@
       <c r="D12" s="30" t="n"/>
       <c r="E12" s="31" t="n"/>
       <c r="F12" s="32">
-        <f>IF(B12="","",IF(E12=TRUE,"✓ Payée",IF(D12&lt;DAY(TODAY()),"⚠ EN RETARD",IF(D12-DAY(TODAY())&lt;=3,"Dans "&amp;(D12-DAY(TODAY()))&amp;" jour(s)","Le "&amp;D12))))</f>
+        <f>IF(B12="","",IF(E12="Oui","Payée",IF(D12&lt;DAY(TODAY()),"En retard",IF((D12-DAY(TODAY()))=0,"Aujourd'hui",IF((D12-DAY(TODAY()))&lt;=3,"Dans "&amp;(D12-DAY(TODAY()))&amp;IF((D12-DAY(TODAY()))&lt;=1," jour"," jours"),"Le "&amp;D12)))))</f>
         <v/>
       </c>
       <c r="G12" s="1" t="n"/>
@@ -4339,7 +4362,7 @@
       <c r="D13" s="30" t="n"/>
       <c r="E13" s="31" t="n"/>
       <c r="F13" s="32">
-        <f>IF(B13="","",IF(E13=TRUE,"✓ Payée",IF(D13&lt;DAY(TODAY()),"⚠ EN RETARD",IF(D13-DAY(TODAY())&lt;=3,"Dans "&amp;(D13-DAY(TODAY()))&amp;" jour(s)","Le "&amp;D13))))</f>
+        <f>IF(B13="","",IF(E13="Oui","Payée",IF(D13&lt;DAY(TODAY()),"En retard",IF((D13-DAY(TODAY()))=0,"Aujourd'hui",IF((D13-DAY(TODAY()))&lt;=3,"Dans "&amp;(D13-DAY(TODAY()))&amp;IF((D13-DAY(TODAY()))&lt;=1," jour"," jours"),"Le "&amp;D13)))))</f>
         <v/>
       </c>
       <c r="G13" s="1" t="n"/>
@@ -4351,7 +4374,7 @@
       <c r="D14" s="30" t="n"/>
       <c r="E14" s="31" t="n"/>
       <c r="F14" s="32">
-        <f>IF(B14="","",IF(E14=TRUE,"✓ Payée",IF(D14&lt;DAY(TODAY()),"⚠ EN RETARD",IF(D14-DAY(TODAY())&lt;=3,"Dans "&amp;(D14-DAY(TODAY()))&amp;" jour(s)","Le "&amp;D14))))</f>
+        <f>IF(B14="","",IF(E14="Oui","Payée",IF(D14&lt;DAY(TODAY()),"En retard",IF((D14-DAY(TODAY()))=0,"Aujourd'hui",IF((D14-DAY(TODAY()))&lt;=3,"Dans "&amp;(D14-DAY(TODAY()))&amp;IF((D14-DAY(TODAY()))&lt;=1," jour"," jours"),"Le "&amp;D14)))))</f>
         <v/>
       </c>
       <c r="G14" s="1" t="n"/>
@@ -4363,7 +4386,7 @@
       <c r="D15" s="30" t="n"/>
       <c r="E15" s="31" t="n"/>
       <c r="F15" s="32">
-        <f>IF(B15="","",IF(E15=TRUE,"✓ Payée",IF(D15&lt;DAY(TODAY()),"⚠ EN RETARD",IF(D15-DAY(TODAY())&lt;=3,"Dans "&amp;(D15-DAY(TODAY()))&amp;" jour(s)","Le "&amp;D15))))</f>
+        <f>IF(B15="","",IF(E15="Oui","Payée",IF(D15&lt;DAY(TODAY()),"En retard",IF((D15-DAY(TODAY()))=0,"Aujourd'hui",IF((D15-DAY(TODAY()))&lt;=3,"Dans "&amp;(D15-DAY(TODAY()))&amp;IF((D15-DAY(TODAY()))&lt;=1," jour"," jours"),"Le "&amp;D15)))))</f>
         <v/>
       </c>
       <c r="G15" s="1" t="n"/>
@@ -4375,7 +4398,7 @@
       <c r="D16" s="30" t="n"/>
       <c r="E16" s="31" t="n"/>
       <c r="F16" s="32">
-        <f>IF(B16="","",IF(E16=TRUE,"✓ Payée",IF(D16&lt;DAY(TODAY()),"⚠ EN RETARD",IF(D16-DAY(TODAY())&lt;=3,"Dans "&amp;(D16-DAY(TODAY()))&amp;" jour(s)","Le "&amp;D16))))</f>
+        <f>IF(B16="","",IF(E16="Oui","Payée",IF(D16&lt;DAY(TODAY()),"En retard",IF((D16-DAY(TODAY()))=0,"Aujourd'hui",IF((D16-DAY(TODAY()))&lt;=3,"Dans "&amp;(D16-DAY(TODAY()))&amp;IF((D16-DAY(TODAY()))&lt;=1," jour"," jours"),"Le "&amp;D16)))))</f>
         <v/>
       </c>
       <c r="G16" s="1" t="n"/>
@@ -4387,7 +4410,7 @@
       <c r="D17" s="30" t="n"/>
       <c r="E17" s="31" t="n"/>
       <c r="F17" s="32">
-        <f>IF(B17="","",IF(E17=TRUE,"✓ Payée",IF(D17&lt;DAY(TODAY()),"⚠ EN RETARD",IF(D17-DAY(TODAY())&lt;=3,"Dans "&amp;(D17-DAY(TODAY()))&amp;" jour(s)","Le "&amp;D17))))</f>
+        <f>IF(B17="","",IF(E17="Oui","Payée",IF(D17&lt;DAY(TODAY()),"En retard",IF((D17-DAY(TODAY()))=0,"Aujourd'hui",IF((D17-DAY(TODAY()))&lt;=3,"Dans "&amp;(D17-DAY(TODAY()))&amp;IF((D17-DAY(TODAY()))&lt;=1," jour"," jours"),"Le "&amp;D17)))))</f>
         <v/>
       </c>
       <c r="G17" s="1" t="n"/>
@@ -4399,7 +4422,7 @@
       <c r="D18" s="30" t="n"/>
       <c r="E18" s="31" t="n"/>
       <c r="F18" s="32">
-        <f>IF(B18="","",IF(E18=TRUE,"✓ Payée",IF(D18&lt;DAY(TODAY()),"⚠ EN RETARD",IF(D18-DAY(TODAY())&lt;=3,"Dans "&amp;(D18-DAY(TODAY()))&amp;" jour(s)","Le "&amp;D18))))</f>
+        <f>IF(B18="","",IF(E18="Oui","Payée",IF(D18&lt;DAY(TODAY()),"En retard",IF((D18-DAY(TODAY()))=0,"Aujourd'hui",IF((D18-DAY(TODAY()))&lt;=3,"Dans "&amp;(D18-DAY(TODAY()))&amp;IF((D18-DAY(TODAY()))&lt;=1," jour"," jours"),"Le "&amp;D18)))))</f>
         <v/>
       </c>
       <c r="G18" s="1" t="n"/>
@@ -4411,7 +4434,7 @@
       <c r="D19" s="30" t="n"/>
       <c r="E19" s="31" t="n"/>
       <c r="F19" s="32">
-        <f>IF(B19="","",IF(E19=TRUE,"✓ Payée",IF(D19&lt;DAY(TODAY()),"⚠ EN RETARD",IF(D19-DAY(TODAY())&lt;=3,"Dans "&amp;(D19-DAY(TODAY()))&amp;" jour(s)","Le "&amp;D19))))</f>
+        <f>IF(B19="","",IF(E19="Oui","Payée",IF(D19&lt;DAY(TODAY()),"En retard",IF((D19-DAY(TODAY()))=0,"Aujourd'hui",IF((D19-DAY(TODAY()))&lt;=3,"Dans "&amp;(D19-DAY(TODAY()))&amp;IF((D19-DAY(TODAY()))&lt;=1," jour"," jours"),"Le "&amp;D19)))))</f>
         <v/>
       </c>
       <c r="G19" s="1" t="n"/>
@@ -4423,7 +4446,7 @@
       <c r="D20" s="30" t="n"/>
       <c r="E20" s="31" t="n"/>
       <c r="F20" s="32">
-        <f>IF(B20="","",IF(E20=TRUE,"✓ Payée",IF(D20&lt;DAY(TODAY()),"⚠ EN RETARD",IF(D20-DAY(TODAY())&lt;=3,"Dans "&amp;(D20-DAY(TODAY()))&amp;" jour(s)","Le "&amp;D20))))</f>
+        <f>IF(B20="","",IF(E20="Oui","Payée",IF(D20&lt;DAY(TODAY()),"En retard",IF((D20-DAY(TODAY()))=0,"Aujourd'hui",IF((D20-DAY(TODAY()))&lt;=3,"Dans "&amp;(D20-DAY(TODAY()))&amp;IF((D20-DAY(TODAY()))&lt;=1," jour"," jours"),"Le "&amp;D20)))))</f>
         <v/>
       </c>
       <c r="G20" s="1" t="n"/>
@@ -4435,7 +4458,7 @@
       <c r="D21" s="30" t="n"/>
       <c r="E21" s="31" t="n"/>
       <c r="F21" s="32">
-        <f>IF(B21="","",IF(E21=TRUE,"✓ Payée",IF(D21&lt;DAY(TODAY()),"⚠ EN RETARD",IF(D21-DAY(TODAY())&lt;=3,"Dans "&amp;(D21-DAY(TODAY()))&amp;" jour(s)","Le "&amp;D21))))</f>
+        <f>IF(B21="","",IF(E21="Oui","Payée",IF(D21&lt;DAY(TODAY()),"En retard",IF((D21-DAY(TODAY()))=0,"Aujourd'hui",IF((D21-DAY(TODAY()))&lt;=3,"Dans "&amp;(D21-DAY(TODAY()))&amp;IF((D21-DAY(TODAY()))&lt;=1," jour"," jours"),"Le "&amp;D21)))))</f>
         <v/>
       </c>
       <c r="G21" s="1" t="n"/>
@@ -4447,7 +4470,7 @@
       <c r="D22" s="30" t="n"/>
       <c r="E22" s="31" t="n"/>
       <c r="F22" s="32">
-        <f>IF(B22="","",IF(E22=TRUE,"✓ Payée",IF(D22&lt;DAY(TODAY()),"⚠ EN RETARD",IF(D22-DAY(TODAY())&lt;=3,"Dans "&amp;(D22-DAY(TODAY()))&amp;" jour(s)","Le "&amp;D22))))</f>
+        <f>IF(B22="","",IF(E22="Oui","Payée",IF(D22&lt;DAY(TODAY()),"En retard",IF((D22-DAY(TODAY()))=0,"Aujourd'hui",IF((D22-DAY(TODAY()))&lt;=3,"Dans "&amp;(D22-DAY(TODAY()))&amp;IF((D22-DAY(TODAY()))&lt;=1," jour"," jours"),"Le "&amp;D22)))))</f>
         <v/>
       </c>
       <c r="G22" s="1" t="n"/>
@@ -4459,7 +4482,7 @@
       <c r="D23" s="30" t="n"/>
       <c r="E23" s="31" t="n"/>
       <c r="F23" s="32">
-        <f>IF(B23="","",IF(E23=TRUE,"✓ Payée",IF(D23&lt;DAY(TODAY()),"⚠ EN RETARD",IF(D23-DAY(TODAY())&lt;=3,"Dans "&amp;(D23-DAY(TODAY()))&amp;" jour(s)","Le "&amp;D23))))</f>
+        <f>IF(B23="","",IF(E23="Oui","Payée",IF(D23&lt;DAY(TODAY()),"En retard",IF((D23-DAY(TODAY()))=0,"Aujourd'hui",IF((D23-DAY(TODAY()))&lt;=3,"Dans "&amp;(D23-DAY(TODAY()))&amp;IF((D23-DAY(TODAY()))&lt;=1," jour"," jours"),"Le "&amp;D23)))))</f>
         <v/>
       </c>
       <c r="G23" s="1" t="n"/>
@@ -4471,7 +4494,7 @@
       <c r="D24" s="30" t="n"/>
       <c r="E24" s="31" t="n"/>
       <c r="F24" s="32">
-        <f>IF(B24="","",IF(E24=TRUE,"✓ Payée",IF(D24&lt;DAY(TODAY()),"⚠ EN RETARD",IF(D24-DAY(TODAY())&lt;=3,"Dans "&amp;(D24-DAY(TODAY()))&amp;" jour(s)","Le "&amp;D24))))</f>
+        <f>IF(B24="","",IF(E24="Oui","Payée",IF(D24&lt;DAY(TODAY()),"En retard",IF((D24-DAY(TODAY()))=0,"Aujourd'hui",IF((D24-DAY(TODAY()))&lt;=3,"Dans "&amp;(D24-DAY(TODAY()))&amp;IF((D24-DAY(TODAY()))&lt;=1," jour"," jours"),"Le "&amp;D24)))))</f>
         <v/>
       </c>
       <c r="G24" s="1" t="n"/>
@@ -4483,7 +4506,7 @@
       <c r="D25" s="30" t="n"/>
       <c r="E25" s="31" t="n"/>
       <c r="F25" s="32">
-        <f>IF(B25="","",IF(E25=TRUE,"✓ Payée",IF(D25&lt;DAY(TODAY()),"⚠ EN RETARD",IF(D25-DAY(TODAY())&lt;=3,"Dans "&amp;(D25-DAY(TODAY()))&amp;" jour(s)","Le "&amp;D25))))</f>
+        <f>IF(B25="","",IF(E25="Oui","Payée",IF(D25&lt;DAY(TODAY()),"En retard",IF((D25-DAY(TODAY()))=0,"Aujourd'hui",IF((D25-DAY(TODAY()))&lt;=3,"Dans "&amp;(D25-DAY(TODAY()))&amp;IF((D25-DAY(TODAY()))&lt;=1," jour"," jours"),"Le "&amp;D25)))))</f>
         <v/>
       </c>
       <c r="G25" s="1" t="n"/>
@@ -4495,7 +4518,7 @@
       <c r="D26" s="30" t="n"/>
       <c r="E26" s="31" t="n"/>
       <c r="F26" s="32">
-        <f>IF(B26="","",IF(E26=TRUE,"✓ Payée",IF(D26&lt;DAY(TODAY()),"⚠ EN RETARD",IF(D26-DAY(TODAY())&lt;=3,"Dans "&amp;(D26-DAY(TODAY()))&amp;" jour(s)","Le "&amp;D26))))</f>
+        <f>IF(B26="","",IF(E26="Oui","Payée",IF(D26&lt;DAY(TODAY()),"En retard",IF((D26-DAY(TODAY()))=0,"Aujourd'hui",IF((D26-DAY(TODAY()))&lt;=3,"Dans "&amp;(D26-DAY(TODAY()))&amp;IF((D26-DAY(TODAY()))&lt;=1," jour"," jours"),"Le "&amp;D26)))))</f>
         <v/>
       </c>
       <c r="G26" s="1" t="n"/>
@@ -4507,7 +4530,7 @@
       <c r="D27" s="30" t="n"/>
       <c r="E27" s="31" t="n"/>
       <c r="F27" s="32">
-        <f>IF(B27="","",IF(E27=TRUE,"✓ Payée",IF(D27&lt;DAY(TODAY()),"⚠ EN RETARD",IF(D27-DAY(TODAY())&lt;=3,"Dans "&amp;(D27-DAY(TODAY()))&amp;" jour(s)","Le "&amp;D27))))</f>
+        <f>IF(B27="","",IF(E27="Oui","Payée",IF(D27&lt;DAY(TODAY()),"En retard",IF((D27-DAY(TODAY()))=0,"Aujourd'hui",IF((D27-DAY(TODAY()))&lt;=3,"Dans "&amp;(D27-DAY(TODAY()))&amp;IF((D27-DAY(TODAY()))&lt;=1," jour"," jours"),"Le "&amp;D27)))))</f>
         <v/>
       </c>
       <c r="G27" s="1" t="n"/>
@@ -4519,7 +4542,7 @@
       <c r="D28" s="30" t="n"/>
       <c r="E28" s="31" t="n"/>
       <c r="F28" s="32">
-        <f>IF(B28="","",IF(E28=TRUE,"✓ Payée",IF(D28&lt;DAY(TODAY()),"⚠ EN RETARD",IF(D28-DAY(TODAY())&lt;=3,"Dans "&amp;(D28-DAY(TODAY()))&amp;" jour(s)","Le "&amp;D28))))</f>
+        <f>IF(B28="","",IF(E28="Oui","Payée",IF(D28&lt;DAY(TODAY()),"En retard",IF((D28-DAY(TODAY()))=0,"Aujourd'hui",IF((D28-DAY(TODAY()))&lt;=3,"Dans "&amp;(D28-DAY(TODAY()))&amp;IF((D28-DAY(TODAY()))&lt;=1," jour"," jours"),"Le "&amp;D28)))))</f>
         <v/>
       </c>
       <c r="G28" s="1" t="n"/>
@@ -4531,7 +4554,7 @@
       <c r="D29" s="30" t="n"/>
       <c r="E29" s="31" t="n"/>
       <c r="F29" s="32">
-        <f>IF(B29="","",IF(E29=TRUE,"✓ Payée",IF(D29&lt;DAY(TODAY()),"⚠ EN RETARD",IF(D29-DAY(TODAY())&lt;=3,"Dans "&amp;(D29-DAY(TODAY()))&amp;" jour(s)","Le "&amp;D29))))</f>
+        <f>IF(B29="","",IF(E29="Oui","Payée",IF(D29&lt;DAY(TODAY()),"En retard",IF((D29-DAY(TODAY()))=0,"Aujourd'hui",IF((D29-DAY(TODAY()))&lt;=3,"Dans "&amp;(D29-DAY(TODAY()))&amp;IF((D29-DAY(TODAY()))&lt;=1," jour"," jours"),"Le "&amp;D29)))))</f>
         <v/>
       </c>
       <c r="G29" s="1" t="n"/>
@@ -4543,7 +4566,7 @@
       <c r="D30" s="30" t="n"/>
       <c r="E30" s="31" t="n"/>
       <c r="F30" s="32">
-        <f>IF(B30="","",IF(E30=TRUE,"✓ Payée",IF(D30&lt;DAY(TODAY()),"⚠ EN RETARD",IF(D30-DAY(TODAY())&lt;=3,"Dans "&amp;(D30-DAY(TODAY()))&amp;" jour(s)","Le "&amp;D30))))</f>
+        <f>IF(B30="","",IF(E30="Oui","Payée",IF(D30&lt;DAY(TODAY()),"En retard",IF((D30-DAY(TODAY()))=0,"Aujourd'hui",IF((D30-DAY(TODAY()))&lt;=3,"Dans "&amp;(D30-DAY(TODAY()))&amp;IF((D30-DAY(TODAY()))&lt;=1," jour"," jours"),"Le "&amp;D30)))))</f>
         <v/>
       </c>
       <c r="G30" s="1" t="n"/>
@@ -4992,18 +5015,18 @@
   </sheetData>
   <conditionalFormatting sqref="F6:F30">
     <cfRule type="expression" priority="1" dxfId="3">
-      <formula>LEFT($F6,1)="✓"</formula>
+      <formula>$F6="Payée"</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="0">
-      <formula>LEFT($F6,1)="⚠"</formula>
+      <formula>$F6="En retard"</formula>
     </cfRule>
     <cfRule type="expression" priority="3" dxfId="4">
-      <formula>AND(LEFT($F6,4)="Dans",($D6-DAY(TODAY()))&lt;=3)</formula>
+      <formula>OR(LEFT($F6,4)="Dans",$F6="Aujourd'hui")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation sqref="E6:E30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"TRUE,FALSE"</formula1>
+      <formula1>"Oui,Non"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5056,7 +5079,7 @@
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Envie de l’acheter ? Mettez-le ici. Si l’envie est toujours là dans 48 heures, allez-y.</t>
+          <t>Notez ce que vous voulez acheter. Si l'envie est toujours là 48 heures plus tard, allez-y.</t>
         </is>
       </c>
       <c r="C3" s="1" t="n"/>
@@ -5122,7 +5145,7 @@
         <v>46290</v>
       </c>
       <c r="E6" s="34">
-        <f>IF(B6="","",IF(F6&lt;&gt;"",F6,IF(TODAY()-D6&gt;=2,"✓ 48 h passées : achetez seulement si l’envie est toujours là","⏳ Encore "&amp;(2-(TODAY()-D6))&amp;" jour(s) à attendre")))</f>
+        <f>IF(B6="","",IF(F6&lt;&gt;"",F6,IF(TODAY()-D6&gt;=2,"48 heures passées : achetez si l'envie est toujours là","Encore "&amp;(2-(TODAY()-D6))&amp;IF((2-(TODAY()-D6))&lt;=1," jour"," jours")&amp;" à attendre")))</f>
         <v/>
       </c>
       <c r="F6" s="31" t="inlineStr"/>
@@ -5146,7 +5169,7 @@
         <v>46292</v>
       </c>
       <c r="E7" s="34">
-        <f>IF(B7="","",IF(F7&lt;&gt;"",F7,IF(TODAY()-D7&gt;=2,"✓ 48 h passées : achetez seulement si l’envie est toujours là","⏳ Encore "&amp;(2-(TODAY()-D7))&amp;" jour(s) à attendre")))</f>
+        <f>IF(B7="","",IF(F7&lt;&gt;"",F7,IF(TODAY()-D7&gt;=2,"48 heures passées : achetez si l'envie est toujours là","Encore "&amp;(2-(TODAY()-D7))&amp;IF((2-(TODAY()-D7))&lt;=1," jour"," jours")&amp;" à attendre")))</f>
         <v/>
       </c>
       <c r="F7" s="31" t="inlineStr"/>
@@ -5166,7 +5189,7 @@
         <v>46287</v>
       </c>
       <c r="E8" s="34">
-        <f>IF(B8="","",IF(F8&lt;&gt;"",F8,IF(TODAY()-D8&gt;=2,"✓ 48 h passées : achetez seulement si l’envie est toujours là","⏳ Encore "&amp;(2-(TODAY()-D8))&amp;" jour(s) à attendre")))</f>
+        <f>IF(B8="","",IF(F8&lt;&gt;"",F8,IF(TODAY()-D8&gt;=2,"48 heures passées : achetez si l'envie est toujours là","Encore "&amp;(2-(TODAY()-D8))&amp;IF((2-(TODAY()-D8))&lt;=1," jour"," jours")&amp;" à attendre")))</f>
         <v/>
       </c>
       <c r="F8" s="31" t="inlineStr">
@@ -5190,7 +5213,7 @@
         <v>46284</v>
       </c>
       <c r="E9" s="34">
-        <f>IF(B9="","",IF(F9&lt;&gt;"",F9,IF(TODAY()-D9&gt;=2,"✓ 48 h passées : achetez seulement si l’envie est toujours là","⏳ Encore "&amp;(2-(TODAY()-D9))&amp;" jour(s) à attendre")))</f>
+        <f>IF(B9="","",IF(F9&lt;&gt;"",F9,IF(TODAY()-D9&gt;=2,"48 heures passées : achetez si l'envie est toujours là","Encore "&amp;(2-(TODAY()-D9))&amp;IF((2-(TODAY()-D9))&lt;=1," jour"," jours")&amp;" à attendre")))</f>
         <v/>
       </c>
       <c r="F9" s="31" t="inlineStr">
@@ -5214,7 +5237,7 @@
         <v>46293</v>
       </c>
       <c r="E10" s="34">
-        <f>IF(B10="","",IF(F10&lt;&gt;"",F10,IF(TODAY()-D10&gt;=2,"✓ 48 h passées : achetez seulement si l’envie est toujours là","⏳ Encore "&amp;(2-(TODAY()-D10))&amp;" jour(s) à attendre")))</f>
+        <f>IF(B10="","",IF(F10&lt;&gt;"",F10,IF(TODAY()-D10&gt;=2,"48 heures passées : achetez si l'envie est toujours là","Encore "&amp;(2-(TODAY()-D10))&amp;IF((2-(TODAY()-D10))&lt;=1," jour"," jours")&amp;" à attendre")))</f>
         <v/>
       </c>
       <c r="F10" s="31" t="inlineStr"/>
@@ -5226,7 +5249,7 @@
       <c r="C11" s="28" t="n"/>
       <c r="D11" s="29" t="n"/>
       <c r="E11" s="34">
-        <f>IF(B11="","",IF(F11&lt;&gt;"",F11,IF(TODAY()-D11&gt;=2,"✓ 48 h passées : achetez seulement si l’envie est toujours là","⏳ Encore "&amp;(2-(TODAY()-D11))&amp;" jour(s) à attendre")))</f>
+        <f>IF(B11="","",IF(F11&lt;&gt;"",F11,IF(TODAY()-D11&gt;=2,"48 heures passées : achetez si l'envie est toujours là","Encore "&amp;(2-(TODAY()-D11))&amp;IF((2-(TODAY()-D11))&lt;=1," jour"," jours")&amp;" à attendre")))</f>
         <v/>
       </c>
       <c r="F11" s="31" t="n"/>
@@ -5238,7 +5261,7 @@
       <c r="C12" s="28" t="n"/>
       <c r="D12" s="29" t="n"/>
       <c r="E12" s="34">
-        <f>IF(B12="","",IF(F12&lt;&gt;"",F12,IF(TODAY()-D12&gt;=2,"✓ 48 h passées : achetez seulement si l’envie est toujours là","⏳ Encore "&amp;(2-(TODAY()-D12))&amp;" jour(s) à attendre")))</f>
+        <f>IF(B12="","",IF(F12&lt;&gt;"",F12,IF(TODAY()-D12&gt;=2,"48 heures passées : achetez si l'envie est toujours là","Encore "&amp;(2-(TODAY()-D12))&amp;IF((2-(TODAY()-D12))&lt;=1," jour"," jours")&amp;" à attendre")))</f>
         <v/>
       </c>
       <c r="F12" s="31" t="n"/>
@@ -5250,7 +5273,7 @@
       <c r="C13" s="28" t="n"/>
       <c r="D13" s="29" t="n"/>
       <c r="E13" s="34">
-        <f>IF(B13="","",IF(F13&lt;&gt;"",F13,IF(TODAY()-D13&gt;=2,"✓ 48 h passées : achetez seulement si l’envie est toujours là","⏳ Encore "&amp;(2-(TODAY()-D13))&amp;" jour(s) à attendre")))</f>
+        <f>IF(B13="","",IF(F13&lt;&gt;"",F13,IF(TODAY()-D13&gt;=2,"48 heures passées : achetez si l'envie est toujours là","Encore "&amp;(2-(TODAY()-D13))&amp;IF((2-(TODAY()-D13))&lt;=1," jour"," jours")&amp;" à attendre")))</f>
         <v/>
       </c>
       <c r="F13" s="31" t="n"/>
@@ -5262,7 +5285,7 @@
       <c r="C14" s="28" t="n"/>
       <c r="D14" s="29" t="n"/>
       <c r="E14" s="34">
-        <f>IF(B14="","",IF(F14&lt;&gt;"",F14,IF(TODAY()-D14&gt;=2,"✓ 48 h passées : achetez seulement si l’envie est toujours là","⏳ Encore "&amp;(2-(TODAY()-D14))&amp;" jour(s) à attendre")))</f>
+        <f>IF(B14="","",IF(F14&lt;&gt;"",F14,IF(TODAY()-D14&gt;=2,"48 heures passées : achetez si l'envie est toujours là","Encore "&amp;(2-(TODAY()-D14))&amp;IF((2-(TODAY()-D14))&lt;=1," jour"," jours")&amp;" à attendre")))</f>
         <v/>
       </c>
       <c r="F14" s="31" t="n"/>
@@ -5274,7 +5297,7 @@
       <c r="C15" s="28" t="n"/>
       <c r="D15" s="29" t="n"/>
       <c r="E15" s="34">
-        <f>IF(B15="","",IF(F15&lt;&gt;"",F15,IF(TODAY()-D15&gt;=2,"✓ 48 h passées : achetez seulement si l’envie est toujours là","⏳ Encore "&amp;(2-(TODAY()-D15))&amp;" jour(s) à attendre")))</f>
+        <f>IF(B15="","",IF(F15&lt;&gt;"",F15,IF(TODAY()-D15&gt;=2,"48 heures passées : achetez si l'envie est toujours là","Encore "&amp;(2-(TODAY()-D15))&amp;IF((2-(TODAY()-D15))&lt;=1," jour"," jours")&amp;" à attendre")))</f>
         <v/>
       </c>
       <c r="F15" s="31" t="n"/>
@@ -5286,7 +5309,7 @@
       <c r="C16" s="28" t="n"/>
       <c r="D16" s="29" t="n"/>
       <c r="E16" s="34">
-        <f>IF(B16="","",IF(F16&lt;&gt;"",F16,IF(TODAY()-D16&gt;=2,"✓ 48 h passées : achetez seulement si l’envie est toujours là","⏳ Encore "&amp;(2-(TODAY()-D16))&amp;" jour(s) à attendre")))</f>
+        <f>IF(B16="","",IF(F16&lt;&gt;"",F16,IF(TODAY()-D16&gt;=2,"48 heures passées : achetez si l'envie est toujours là","Encore "&amp;(2-(TODAY()-D16))&amp;IF((2-(TODAY()-D16))&lt;=1," jour"," jours")&amp;" à attendre")))</f>
         <v/>
       </c>
       <c r="F16" s="31" t="n"/>
@@ -5298,7 +5321,7 @@
       <c r="C17" s="28" t="n"/>
       <c r="D17" s="29" t="n"/>
       <c r="E17" s="34">
-        <f>IF(B17="","",IF(F17&lt;&gt;"",F17,IF(TODAY()-D17&gt;=2,"✓ 48 h passées : achetez seulement si l’envie est toujours là","⏳ Encore "&amp;(2-(TODAY()-D17))&amp;" jour(s) à attendre")))</f>
+        <f>IF(B17="","",IF(F17&lt;&gt;"",F17,IF(TODAY()-D17&gt;=2,"48 heures passées : achetez si l'envie est toujours là","Encore "&amp;(2-(TODAY()-D17))&amp;IF((2-(TODAY()-D17))&lt;=1," jour"," jours")&amp;" à attendre")))</f>
         <v/>
       </c>
       <c r="F17" s="31" t="n"/>
@@ -5310,7 +5333,7 @@
       <c r="C18" s="28" t="n"/>
       <c r="D18" s="29" t="n"/>
       <c r="E18" s="34">
-        <f>IF(B18="","",IF(F18&lt;&gt;"",F18,IF(TODAY()-D18&gt;=2,"✓ 48 h passées : achetez seulement si l’envie est toujours là","⏳ Encore "&amp;(2-(TODAY()-D18))&amp;" jour(s) à attendre")))</f>
+        <f>IF(B18="","",IF(F18&lt;&gt;"",F18,IF(TODAY()-D18&gt;=2,"48 heures passées : achetez si l'envie est toujours là","Encore "&amp;(2-(TODAY()-D18))&amp;IF((2-(TODAY()-D18))&lt;=1," jour"," jours")&amp;" à attendre")))</f>
         <v/>
       </c>
       <c r="F18" s="31" t="n"/>
@@ -5322,7 +5345,7 @@
       <c r="C19" s="28" t="n"/>
       <c r="D19" s="29" t="n"/>
       <c r="E19" s="34">
-        <f>IF(B19="","",IF(F19&lt;&gt;"",F19,IF(TODAY()-D19&gt;=2,"✓ 48 h passées : achetez seulement si l’envie est toujours là","⏳ Encore "&amp;(2-(TODAY()-D19))&amp;" jour(s) à attendre")))</f>
+        <f>IF(B19="","",IF(F19&lt;&gt;"",F19,IF(TODAY()-D19&gt;=2,"48 heures passées : achetez si l'envie est toujours là","Encore "&amp;(2-(TODAY()-D19))&amp;IF((2-(TODAY()-D19))&lt;=1," jour"," jours")&amp;" à attendre")))</f>
         <v/>
       </c>
       <c r="F19" s="31" t="n"/>
@@ -5334,7 +5357,7 @@
       <c r="C20" s="28" t="n"/>
       <c r="D20" s="29" t="n"/>
       <c r="E20" s="34">
-        <f>IF(B20="","",IF(F20&lt;&gt;"",F20,IF(TODAY()-D20&gt;=2,"✓ 48 h passées : achetez seulement si l’envie est toujours là","⏳ Encore "&amp;(2-(TODAY()-D20))&amp;" jour(s) à attendre")))</f>
+        <f>IF(B20="","",IF(F20&lt;&gt;"",F20,IF(TODAY()-D20&gt;=2,"48 heures passées : achetez si l'envie est toujours là","Encore "&amp;(2-(TODAY()-D20))&amp;IF((2-(TODAY()-D20))&lt;=1," jour"," jours")&amp;" à attendre")))</f>
         <v/>
       </c>
       <c r="F20" s="31" t="n"/>
@@ -5346,7 +5369,7 @@
       <c r="C21" s="28" t="n"/>
       <c r="D21" s="29" t="n"/>
       <c r="E21" s="34">
-        <f>IF(B21="","",IF(F21&lt;&gt;"",F21,IF(TODAY()-D21&gt;=2,"✓ 48 h passées : achetez seulement si l’envie est toujours là","⏳ Encore "&amp;(2-(TODAY()-D21))&amp;" jour(s) à attendre")))</f>
+        <f>IF(B21="","",IF(F21&lt;&gt;"",F21,IF(TODAY()-D21&gt;=2,"48 heures passées : achetez si l'envie est toujours là","Encore "&amp;(2-(TODAY()-D21))&amp;IF((2-(TODAY()-D21))&lt;=1," jour"," jours")&amp;" à attendre")))</f>
         <v/>
       </c>
       <c r="F21" s="31" t="n"/>
@@ -5358,7 +5381,7 @@
       <c r="C22" s="28" t="n"/>
       <c r="D22" s="29" t="n"/>
       <c r="E22" s="34">
-        <f>IF(B22="","",IF(F22&lt;&gt;"",F22,IF(TODAY()-D22&gt;=2,"✓ 48 h passées : achetez seulement si l’envie est toujours là","⏳ Encore "&amp;(2-(TODAY()-D22))&amp;" jour(s) à attendre")))</f>
+        <f>IF(B22="","",IF(F22&lt;&gt;"",F22,IF(TODAY()-D22&gt;=2,"48 heures passées : achetez si l'envie est toujours là","Encore "&amp;(2-(TODAY()-D22))&amp;IF((2-(TODAY()-D22))&lt;=1," jour"," jours")&amp;" à attendre")))</f>
         <v/>
       </c>
       <c r="F22" s="31" t="n"/>
@@ -5370,7 +5393,7 @@
       <c r="C23" s="28" t="n"/>
       <c r="D23" s="29" t="n"/>
       <c r="E23" s="34">
-        <f>IF(B23="","",IF(F23&lt;&gt;"",F23,IF(TODAY()-D23&gt;=2,"✓ 48 h passées : achetez seulement si l’envie est toujours là","⏳ Encore "&amp;(2-(TODAY()-D23))&amp;" jour(s) à attendre")))</f>
+        <f>IF(B23="","",IF(F23&lt;&gt;"",F23,IF(TODAY()-D23&gt;=2,"48 heures passées : achetez si l'envie est toujours là","Encore "&amp;(2-(TODAY()-D23))&amp;IF((2-(TODAY()-D23))&lt;=1," jour"," jours")&amp;" à attendre")))</f>
         <v/>
       </c>
       <c r="F23" s="31" t="n"/>
@@ -5382,7 +5405,7 @@
       <c r="C24" s="28" t="n"/>
       <c r="D24" s="29" t="n"/>
       <c r="E24" s="34">
-        <f>IF(B24="","",IF(F24&lt;&gt;"",F24,IF(TODAY()-D24&gt;=2,"✓ 48 h passées : achetez seulement si l’envie est toujours là","⏳ Encore "&amp;(2-(TODAY()-D24))&amp;" jour(s) à attendre")))</f>
+        <f>IF(B24="","",IF(F24&lt;&gt;"",F24,IF(TODAY()-D24&gt;=2,"48 heures passées : achetez si l'envie est toujours là","Encore "&amp;(2-(TODAY()-D24))&amp;IF((2-(TODAY()-D24))&lt;=1," jour"," jours")&amp;" à attendre")))</f>
         <v/>
       </c>
       <c r="F24" s="31" t="n"/>
@@ -5394,7 +5417,7 @@
       <c r="C25" s="28" t="n"/>
       <c r="D25" s="29" t="n"/>
       <c r="E25" s="34">
-        <f>IF(B25="","",IF(F25&lt;&gt;"",F25,IF(TODAY()-D25&gt;=2,"✓ 48 h passées : achetez seulement si l’envie est toujours là","⏳ Encore "&amp;(2-(TODAY()-D25))&amp;" jour(s) à attendre")))</f>
+        <f>IF(B25="","",IF(F25&lt;&gt;"",F25,IF(TODAY()-D25&gt;=2,"48 heures passées : achetez si l'envie est toujours là","Encore "&amp;(2-(TODAY()-D25))&amp;IF((2-(TODAY()-D25))&lt;=1," jour"," jours")&amp;" à attendre")))</f>
         <v/>
       </c>
       <c r="F25" s="31" t="n"/>
@@ -5406,7 +5429,7 @@
       <c r="C26" s="28" t="n"/>
       <c r="D26" s="29" t="n"/>
       <c r="E26" s="34">
-        <f>IF(B26="","",IF(F26&lt;&gt;"",F26,IF(TODAY()-D26&gt;=2,"✓ 48 h passées : achetez seulement si l’envie est toujours là","⏳ Encore "&amp;(2-(TODAY()-D26))&amp;" jour(s) à attendre")))</f>
+        <f>IF(B26="","",IF(F26&lt;&gt;"",F26,IF(TODAY()-D26&gt;=2,"48 heures passées : achetez si l'envie est toujours là","Encore "&amp;(2-(TODAY()-D26))&amp;IF((2-(TODAY()-D26))&lt;=1," jour"," jours")&amp;" à attendre")))</f>
         <v/>
       </c>
       <c r="F26" s="31" t="n"/>
@@ -5418,7 +5441,7 @@
       <c r="C27" s="28" t="n"/>
       <c r="D27" s="29" t="n"/>
       <c r="E27" s="34">
-        <f>IF(B27="","",IF(F27&lt;&gt;"",F27,IF(TODAY()-D27&gt;=2,"✓ 48 h passées : achetez seulement si l’envie est toujours là","⏳ Encore "&amp;(2-(TODAY()-D27))&amp;" jour(s) à attendre")))</f>
+        <f>IF(B27="","",IF(F27&lt;&gt;"",F27,IF(TODAY()-D27&gt;=2,"48 heures passées : achetez si l'envie est toujours là","Encore "&amp;(2-(TODAY()-D27))&amp;IF((2-(TODAY()-D27))&lt;=1," jour"," jours")&amp;" à attendre")))</f>
         <v/>
       </c>
       <c r="F27" s="31" t="n"/>
@@ -5430,7 +5453,7 @@
       <c r="C28" s="28" t="n"/>
       <c r="D28" s="29" t="n"/>
       <c r="E28" s="34">
-        <f>IF(B28="","",IF(F28&lt;&gt;"",F28,IF(TODAY()-D28&gt;=2,"✓ 48 h passées : achetez seulement si l’envie est toujours là","⏳ Encore "&amp;(2-(TODAY()-D28))&amp;" jour(s) à attendre")))</f>
+        <f>IF(B28="","",IF(F28&lt;&gt;"",F28,IF(TODAY()-D28&gt;=2,"48 heures passées : achetez si l'envie est toujours là","Encore "&amp;(2-(TODAY()-D28))&amp;IF((2-(TODAY()-D28))&lt;=1," jour"," jours")&amp;" à attendre")))</f>
         <v/>
       </c>
       <c r="F28" s="31" t="n"/>
@@ -5442,7 +5465,7 @@
       <c r="C29" s="28" t="n"/>
       <c r="D29" s="29" t="n"/>
       <c r="E29" s="34">
-        <f>IF(B29="","",IF(F29&lt;&gt;"",F29,IF(TODAY()-D29&gt;=2,"✓ 48 h passées : achetez seulement si l’envie est toujours là","⏳ Encore "&amp;(2-(TODAY()-D29))&amp;" jour(s) à attendre")))</f>
+        <f>IF(B29="","",IF(F29&lt;&gt;"",F29,IF(TODAY()-D29&gt;=2,"48 heures passées : achetez si l'envie est toujours là","Encore "&amp;(2-(TODAY()-D29))&amp;IF((2-(TODAY()-D29))&lt;=1," jour"," jours")&amp;" à attendre")))</f>
         <v/>
       </c>
       <c r="F29" s="31" t="n"/>
@@ -5454,7 +5477,7 @@
       <c r="C30" s="28" t="n"/>
       <c r="D30" s="29" t="n"/>
       <c r="E30" s="34">
-        <f>IF(B30="","",IF(F30&lt;&gt;"",F30,IF(TODAY()-D30&gt;=2,"✓ 48 h passées : achetez seulement si l’envie est toujours là","⏳ Encore "&amp;(2-(TODAY()-D30))&amp;" jour(s) à attendre")))</f>
+        <f>IF(B30="","",IF(F30&lt;&gt;"",F30,IF(TODAY()-D30&gt;=2,"48 heures passées : achetez si l'envie est toujours là","Encore "&amp;(2-(TODAY()-D30))&amp;IF((2-(TODAY()-D30))&lt;=1," jour"," jours")&amp;" à attendre")))</f>
         <v/>
       </c>
       <c r="F30" s="31" t="n"/>
@@ -5904,10 +5927,10 @@
   </sheetData>
   <conditionalFormatting sqref="E6:E30">
     <cfRule type="expression" priority="1" dxfId="4">
-      <formula>LEFT($E6,1)="⏳"</formula>
+      <formula>LEFT($E6,6)="Encore"</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="3">
-      <formula>LEFT($E6,1)="✓"</formula>
+      <formula>LEFT($E6,9)="48 heures"</formula>
     </cfRule>
     <cfRule type="expression" priority="3" dxfId="5">
       <formula>$E6="Renoncé"</formula>
@@ -5953,7 +5976,7 @@
       <c r="A2" s="1" t="n"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Objectifs d’épargne</t>
+          <t>Objectifs d'épargne</t>
         </is>
       </c>
       <c r="C2" s="1" t="n"/>
@@ -5966,7 +5989,7 @@
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Mettez à jour « Déjà épargné » dès que vous mettez de l’argent de côté.</t>
+          <t>Mettez à jour la colonne Déjà épargné dès que vous mettez de l'argent de côté.</t>
         </is>
       </c>
       <c r="C3" s="1" t="n"/>
@@ -6017,7 +6040,7 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="27" t="inlineStr">
         <is>
-          <t>Fonds d’urgence</t>
+          <t>Fonds d'urgence</t>
         </is>
       </c>
       <c r="C6" s="28" t="n">
